--- a/nr-cda-template/ig/StructureDefinition-fr-core-health-care-facility.xlsx
+++ b/nr-cda-template/ig/StructureDefinition-fr-core-health-care-facility.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T14:22:39+00:00</t>
+    <t>2025-02-18T14:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
